--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484828_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484828_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.374599999999999</v>
+        <v>8.517899999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>7.9896</v>
+        <v>7.8737</v>
       </c>
       <c r="F2" t="n">
-        <v>1.385</v>
+        <v>0.6442</v>
       </c>
       <c r="G2" t="n">
         <v>5.0335</v>
@@ -610,13 +610,13 @@
         <v>3.774</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5861</v>
+        <v>-0.2705</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4304</v>
+        <v>-0.5463</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0165</v>
+        <v>0.2758</v>
       </c>
       <c r="V2" t="n">
         <v>0.9244</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.1682</v>
+        <v>3.8775</v>
       </c>
       <c r="E3" t="n">
-        <v>3.2285</v>
+        <v>3.5409</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0602</v>
+        <v>0.3366</v>
       </c>
       <c r="G3" t="n">
         <v>0.383</v>
@@ -688,13 +688,13 @@
         <v>3.2079</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.7618</v>
+        <v>-1.0525</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9036</v>
+        <v>-0.5911</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.8582</v>
+        <v>-0.4614</v>
       </c>
       <c r="V3" t="n">
         <v>3.4148</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7518</v>
+        <v>2.152</v>
       </c>
       <c r="E4" t="n">
-        <v>2.8434</v>
+        <v>3.0585</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.0916</v>
+        <v>-0.9065</v>
       </c>
       <c r="G4" t="n">
         <v>2.6071</v>
@@ -766,13 +766,13 @@
         <v>2.0757</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.5161</v>
+        <v>-1.1159</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.1634</v>
+        <v>-0.9484</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3526</v>
+        <v>-0.1675</v>
       </c>
       <c r="V4" t="n">
         <v>-1.2262</v>
@@ -799,10 +799,10 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.172</v>
+        <v>1.5231</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.054</v>
+        <v>0.2971</v>
       </c>
       <c r="F5" t="n">
         <v>1.2261</v>
@@ -844,10 +844,10 @@
         <v>2.0757</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.0516</v>
+        <v>-0.7005</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.458</v>
+        <v>-0.1069</v>
       </c>
       <c r="U5" t="n">
         <v>-0.5937</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8395</v>
+        <v>1.0486</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6568000000000001</v>
+        <v>-0.5006</v>
       </c>
       <c r="F6" t="n">
-        <v>1.4963</v>
+        <v>1.5492</v>
       </c>
       <c r="G6" t="n">
         <v>1.4073</v>
@@ -922,13 +922,13 @@
         <v>2.2644</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9452</v>
+        <v>-0.7361</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4703</v>
+        <v>-0.3141</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4749</v>
+        <v>-0.422</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1586</v>
+        <v>-0.3735</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.6872</v>
+        <v>-1.1928</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8458</v>
+        <v>0.8193</v>
       </c>
       <c r="G7" t="n">
         <v>-1.7482</v>
@@ -1000,13 +1000,13 @@
         <v>3.3966</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0176</v>
+        <v>-0.5498</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2192</v>
+        <v>-0.2865</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2368</v>
+        <v>-0.2633</v>
       </c>
       <c r="V7" t="n">
         <v>1.547</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1917</v>
+        <v>-1.2207</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4862</v>
+        <v>-0.33</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7055</v>
+        <v>-0.8907</v>
       </c>
       <c r="G8" t="n">
         <v>0.2493</v>
@@ -1078,13 +1078,13 @@
         <v>0.9435</v>
       </c>
       <c r="S8" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.0581</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0465</v>
+        <v>0.1098</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1335</v>
+        <v>-0.0517</v>
       </c>
       <c r="V8" t="n">
         <v>-1.528</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-5.3993</v>
+        <v>-4.7694</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.0072</v>
+        <v>-2.6947</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.3922</v>
+        <v>-2.0747</v>
       </c>
       <c r="G9" t="n">
         <v>-2.0376</v>
@@ -1156,13 +1156,13 @@
         <v>1.1322</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8712</v>
+        <v>-0.2413</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4921</v>
+        <v>-0.1796</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3791</v>
+        <v>-0.0617</v>
       </c>
       <c r="V9" t="n">
         <v>-1.547</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>9.873699999999999</v>
+        <v>10.7555</v>
       </c>
       <c r="E10" t="n">
-        <v>9.1701</v>
+        <v>10.0521</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7037000000000002</v>
+        <v>0.7035000000000002</v>
       </c>
       <c r="G10" t="n">
         <v>7.174599999999999</v>
@@ -1234,13 +1234,13 @@
         <v>18.87</v>
       </c>
       <c r="S10" t="n">
-        <v>-5.4904</v>
+        <v>-4.608499999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>-3.7451</v>
+        <v>-2.8631</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.7453</v>
+        <v>-1.7455</v>
       </c>
       <c r="V10" t="n">
         <v>1.585</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>4.2705</v>
+        <v>3.633</v>
       </c>
       <c r="E11" t="n">
-        <v>6.4549</v>
+        <v>5.4806</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.1844</v>
+        <v>-1.8476</v>
       </c>
       <c r="G11" t="n">
         <v>0.4448</v>
@@ -1312,13 +1312,13 @@
         <v>1.887</v>
       </c>
       <c r="S11" t="n">
-        <v>2.2785</v>
+        <v>1.641</v>
       </c>
       <c r="T11" t="n">
-        <v>1.6112</v>
+        <v>0.6369</v>
       </c>
       <c r="U11" t="n">
-        <v>0.6673</v>
+        <v>1.0041</v>
       </c>
       <c r="V11" t="n">
         <v>-0.3398</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5767</v>
+        <v>0.6741</v>
       </c>
       <c r="E12" t="n">
-        <v>1.8332</v>
+        <v>1.9306</v>
       </c>
       <c r="F12" t="n">
         <v>-1.2565</v>
@@ -1390,10 +1390,10 @@
         <v>0.1887</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0588</v>
+        <v>0.0386</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0588</v>
+        <v>0.0386</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2226</v>
+        <v>0.4259</v>
       </c>
       <c r="E13" t="n">
-        <v>1.1446</v>
+        <v>0.8522999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.9219000000000001</v>
+        <v>-0.4264</v>
       </c>
       <c r="G13" t="n">
         <v>0.166</v>
@@ -1468,13 +1468,13 @@
         <v>2.2644</v>
       </c>
       <c r="S13" t="n">
-        <v>1.2644</v>
+        <v>1.4677</v>
       </c>
       <c r="T13" t="n">
-        <v>1.0792</v>
+        <v>0.7869</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1852</v>
+        <v>0.6808</v>
       </c>
       <c r="V13" t="n">
         <v>0.3018</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.192</v>
+        <v>0.281</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0454</v>
+        <v>0.2403</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1466</v>
+        <v>0.0408</v>
       </c>
       <c r="G14" t="n">
         <v>0.4171</v>
@@ -1546,13 +1546,13 @@
         <v>0.3774</v>
       </c>
       <c r="S14" t="n">
-        <v>0.341</v>
+        <v>0.43</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0465</v>
+        <v>0.1484</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3874</v>
+        <v>0.2816</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. ORTOLA TOMAS</t>
+          <t>A. KLEINJAN RODRIGUEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.4948</v>
+        <v>-0.2201</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.1286</v>
+        <v>1.0558</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.3662</v>
+        <v>-1.2759</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.4077</v>
+        <v>-0.0083</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2418</v>
+        <v>0.9336</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.6496</v>
+        <v>-0.9419999999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0477</v>
+        <v>3.1052</v>
       </c>
       <c r="K15" t="n">
-        <v>0.6973</v>
+        <v>1.7961</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.6496</v>
+        <v>1.3091</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.4555</v>
+        <v>-3.1135</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4555</v>
+        <v>-0.8624000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>-2.2511</v>
       </c>
       <c r="P15" t="n">
-        <v>0.3774</v>
+        <v>-2.2644</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-3.774</v>
       </c>
       <c r="R15" t="n">
-        <v>0.3774</v>
+        <v>1.5096</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1581</v>
+        <v>0.5057</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1764</v>
+        <v>0.1776</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3345</v>
+        <v>0.3281</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.6226</v>
+        <v>1.547</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.547</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.6226</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. KLEINJAN RODRIGUEZ</t>
+          <t>J. ORTOLA TOMAS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.878</v>
+        <v>-0.4851</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7635</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.6415</v>
+        <v>-0.5513</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.0083</v>
+        <v>-0.4077</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9336</v>
+        <v>0.2418</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.9419999999999999</v>
+        <v>-0.6496</v>
       </c>
       <c r="J16" t="n">
-        <v>3.1052</v>
+        <v>0.0477</v>
       </c>
       <c r="K16" t="n">
-        <v>1.7961</v>
+        <v>0.6973</v>
       </c>
       <c r="L16" t="n">
-        <v>1.3091</v>
+        <v>-0.6496</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.1135</v>
+        <v>-0.4555</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.8624000000000001</v>
+        <v>-0.4555</v>
       </c>
       <c r="O16" t="n">
-        <v>-2.2511</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>-2.2644</v>
+        <v>0.3774</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.774</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5096</v>
+        <v>0.3774</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1523</v>
+        <v>0.1678</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1147</v>
+        <v>0.0185</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0376</v>
+        <v>0.1493</v>
       </c>
       <c r="V16" t="n">
-        <v>1.547</v>
+        <v>-0.6226</v>
       </c>
       <c r="W16" t="n">
-        <v>1.547</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.6226</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.0413</v>
+        <v>-0.6901</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.2985</v>
+        <v>-0.1036</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.7429</v>
+        <v>-0.5865</v>
       </c>
       <c r="G17" t="n">
         <v>-0.363</v>
@@ -1780,13 +1780,13 @@
         <v>0.5661</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.301</v>
+        <v>0.0503</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1176</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1834</v>
+        <v>-0.027</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.012</v>
+        <v>-1.8074</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.9067</v>
+        <v>-1.517</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1053</v>
+        <v>-0.2905</v>
       </c>
       <c r="G18" t="n">
         <v>-0.0944</v>
@@ -1858,13 +1858,13 @@
         <v>0.7548</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1581</v>
+        <v>0.3627</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.823</v>
+        <v>-0.4333</v>
       </c>
       <c r="U18" t="n">
-        <v>0.9812</v>
+        <v>0.796</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.6991</v>
+        <v>-2.2708</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.8711</v>
+        <v>-2.6762</v>
       </c>
       <c r="F19" t="n">
-        <v>0.172</v>
+        <v>0.4054</v>
       </c>
       <c r="G19" t="n">
         <v>-0.9581</v>
@@ -1936,13 +1936,13 @@
         <v>1.6983</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0053</v>
+        <v>0.4229</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5262</v>
+        <v>-0.3313</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5209</v>
+        <v>0.7543</v>
       </c>
       <c r="V19" t="n">
         <v>-1.547</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.6395</v>
+        <v>-3.0153</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.2425</v>
+        <v>-2.145</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.397</v>
+        <v>-0.8703</v>
       </c>
       <c r="G20" t="n">
         <v>-2.6616</v>
@@ -2014,13 +2014,13 @@
         <v>1.1322</v>
       </c>
       <c r="S20" t="n">
-        <v>0.07870000000000001</v>
+        <v>0.7029</v>
       </c>
       <c r="T20" t="n">
-        <v>0.074</v>
+        <v>0.1715</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0047</v>
+        <v>0.5314</v>
       </c>
       <c r="V20" t="n">
         <v>-0.3018</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.3709</v>
+        <v>-4.4503</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.4978</v>
+        <v>-3.8875</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8732</v>
+        <v>-0.5628</v>
       </c>
       <c r="G21" t="n">
         <v>-4.7789</v>
@@ -2092,13 +2092,13 @@
         <v>1.5096</v>
       </c>
       <c r="S21" t="n">
-        <v>1.7289</v>
+        <v>1.6495</v>
       </c>
       <c r="T21" t="n">
-        <v>0.8441</v>
+        <v>0.4543</v>
       </c>
       <c r="U21" t="n">
-        <v>0.8848</v>
+        <v>1.1952</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-9.873799999999999</v>
+        <v>-7.9251</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.7036000000000002</v>
+        <v>-0.7034999999999996</v>
       </c>
       <c r="F22" t="n">
-        <v>-9.170300000000001</v>
+        <v>-7.2216</v>
       </c>
       <c r="G22" t="n">
         <v>-7.174700000000001</v>
@@ -2170,13 +2170,13 @@
         <v>12.2655</v>
       </c>
       <c r="S22" t="n">
-        <v>5.4903</v>
+        <v>7.4391</v>
       </c>
       <c r="T22" t="n">
-        <v>1.7453</v>
+        <v>1.7454</v>
       </c>
       <c r="U22" t="n">
-        <v>3.745</v>
+        <v>5.6938</v>
       </c>
       <c r="V22" t="n">
         <v>-1.585</v>
